--- a/Iteration-3/UAT-Template.xlsx
+++ b/Iteration-3/UAT-Template.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="52">
   <si>
     <t xml:space="preserve">User Acceptance Test Plan</t>
   </si>
@@ -28,19 +28,19 @@
     <t xml:space="preserve">Project Name</t>
   </si>
   <si>
-    <t xml:space="preserve">Haukainga - Home Winds</t>
+    <t xml:space="preserve">Agile Project – Smart watch E-commerce site</t>
   </si>
   <si>
     <t xml:space="preserve">Project Client</t>
   </si>
   <si>
-    <t xml:space="preserve">Huia Te Kanua</t>
+    <t xml:space="preserve">EIT</t>
   </si>
   <si>
     <t xml:space="preserve">Name of Tester/s:</t>
   </si>
   <si>
-    <t xml:space="preserve">AgentBob</t>
+    <t xml:space="preserve">Euan, Zaine, Austin</t>
   </si>
   <si>
     <t xml:space="preserve">Test ID</t>
@@ -70,37 +70,45 @@
     <t xml:space="preserve">COMPONENT/MODULE 1: </t>
   </si>
   <si>
-    <t xml:space="preserve">Base WordPress and Plugins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WordPress Plugin and Theme functionality</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Install plugins and selected theme. Test plugin features and theme design. See if plugin features are successfully connected and modifying the database records.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plugins perform as required and intereact with the database as required. Theme appears as expected and can be modified easily.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Administrator login and features</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Create two administrator accounts with identical privilages for dual development</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Both administrator accounts have access to all WordPress and plugin features as well as a database accessbility.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User roles and restrictions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generate a login form to create standard users, as well as appoint property users via an admin interface. Using plugin content restriction, hide property management from standard users.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Standard users and property users can be created. Standard users cannot interact with property management.</t>
+    <t xml:space="preserve">Navigation &amp; links</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navigation menu functionality</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Load each page (Home, Products, About, Contact, Orders).
+2. Click each navigation link and verify the destination page title/URL matches.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All 5 nav links clicked across all pages.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each navigation link loads the correct page without 404 errors. Active page is highlighted.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contact form contains 4 input fields (Full Name, Email, Phone number, Message) and a SEND button. Same form appears on both contact.html and index.html.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Footer consistency &amp; social links</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Scroll to footer on each page.
+2. Verify footer content: About text, contact details, subscription form, social icons, copyright.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All 5 pages inspected.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Footer is consistently displayed across all pages with: About section, contact info (Location, phone, email), Subscribe form, social media icons, copyright notice.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Footer identical on all pages. Contains all expected elements. Copyright displays HTML Template attribution.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navbar brand text differs on orders.html ('Timups' vs 'Agile-Project') - minor inconsistency.</t>
   </si>
   <si>
     <t xml:space="preserve">COMPONENT/MODULE 2: </t>
@@ -109,52 +117,39 @@
     <t xml:space="preserve">Custom Plugin Functionality</t>
   </si>
   <si>
-    <t xml:space="preserve">Database Queries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Create test functions and test data to perform Insert, Updates, and Deletes on the user, property, booking, and review table. Perform DML statements in the order of Insert, Update, then Delete, ensuring all test data is deleted before continueing.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Single entries for each table defined within test functions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Database entries are modified as requested, and test functions return true. Test data is no longer present in the database</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HTTP Requests</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Create an HTML form with a POST method. Retrieve this data with PHP then display this data.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Form entries with varied inputs such as special characters or SQL statements</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All data retrieved is equal to what was given. Any special cases including SQL statements are converted to plain string.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">File Uploads</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Create an HTML form to upload only images files, uploading these to a file as well as stored via hash function in the database. Display this image on screen after upload and storage.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Only image file types</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Only accepts files of a certain type as size. Images are stored correctly and can be retrieved and displayed.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Property and Review Read</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Display a single property as well as all reviews and details. Display all propertys with brief information and no reviews.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test Properties and reviews</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All properties are viewed and can be filter as a list view. Individual properties can be viewed and display all reviews and information in a separate view.</t>
+    <t xml:space="preserve">Product catalog display</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Navigate to Products page.
+2. Count product cards.
+3. Verify each card has product image, name, price, and badge.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 product cards on page.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All 7 products display correctly with: product image (w1-w6.png), name 'Smartwatch', price ($300, $125, $110, $145, $195, $170, $230), and badge (Featured/New).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 products displayed. Images load. All prices and badges visible. Featured badge on first product ($300), New badges on all others.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Home page product showcase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Load home page.
+2. Scroll to 'Latest Watches' section.
+3. Verify product grid matches Products page.
+4. Click 'View All' link.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Home page product section.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Home page displays same 7 products in identical layout. 'View All' link is present and navigates to products page.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">View All links on home page use empty href; consider linking to products.html.</t>
   </si>
   <si>
     <t xml:space="preserve">COMPONENT/MODULE 3: </t>
@@ -163,31 +158,38 @@
     <t xml:space="preserve">UI &amp; UX</t>
   </si>
   <si>
-    <t xml:space="preserve">Accessibility</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Design each wordpress page and view to be accessible on any device prioritising PC and smart phone resolutions.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pages change appropriately maintaining their theme and general appearance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Read Data Appearance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Display retrieved data showing all information, data display is reformatted when the display viewport changes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data shown is correct and in full. Display adheres to chosen theme and general appearance.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Links</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Develop all links in an obvious and understandable manner.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All links operate as expected, redirecting to the correct location or displaying the correct information. Links purpose is made obvious to the average user.</t>
+    <t xml:space="preserve">Orders page – Order history &amp; summary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Navigate to Orders page.
+2. Verify order header (Order Number, Date, Total, Shipped To).
+3. Verify status indicator.
+4. Verify order items with images, colors, sizes.
+5. Verify Order Summary calculations.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 sample order with 2 line items.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orders display: order ID (#A915AFLE4FO), date (Oct 4th, 2021), total ($19.54 header), status (Shipped with delivery estimate), item details, and summary (Subtotal $54.97, Tax $4.30, Shipping FREE, Gift -$5.55, Total $53.65).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Order displayed with all fields. Status shows 'Shipped' in green with delivery window. Summary calculations present and consistent. Track Shipment, Buy It Again, Request a Return buttons visible.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contact form presence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Navigate to Contact page.
+2. Verify form fields: Full Name, Email, Phone number, Message.
+3. Verify SEND button.
+4. Verify the same form appears on home page.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contact and Home page inspected.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Both pages have the contact form with all 4 fields and SEND button. Form action is empty (#) - no backend processing.</t>
   </si>
 </sst>
 </file>
@@ -197,7 +199,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -301,6 +303,11 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
@@ -322,10 +329,16 @@
     <font>
       <b val="true"/>
       <sz val="18"/>
-      <color rgb="FF00B050"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="18"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -499,7 +512,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -507,136 +520,164 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="40">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="2" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="2" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="3" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="3" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="4" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="4" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="5" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="5" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="5" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="5" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="0" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="0" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="4" borderId="6" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="4" borderId="6" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="4" borderId="7" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="4" borderId="7" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="4" borderId="8" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="8" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="4" borderId="7" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="4" borderId="7" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="4" borderId="9" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="4" borderId="9" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="10" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="10" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="11" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="11" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="3" borderId="12" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="3" borderId="12" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="13" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="13" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="14" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="14" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="2" borderId="14" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="15" fillId="2" borderId="14" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="15" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="14" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="3" borderId="14" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="2" borderId="15" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="3" borderId="14" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="16" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="16" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="3" borderId="14" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="3" borderId="14" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="10" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="2" borderId="16" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="12" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="15" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="3" borderId="14" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="10" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="10" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="12" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="10" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="11" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="11" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="5" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="2" borderId="5" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="2" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="2" borderId="2" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="2" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="5" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -702,7 +743,7 @@
       <rgbColor rgb="FF666699"/>
       <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF00B050"/>
+      <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
       <rgbColor rgb="FF993300"/>
@@ -894,442 +935,438 @@
   <dimension ref="A1:J23"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="28.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="26.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="32.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="27.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="49.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="37.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="13.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="18.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="28.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="26.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="32.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="27.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="49.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="37.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="13.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="18.29"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="29.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
-      <c r="C1" s="2" t="s">
+      <c r="A1" s="2"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="4" t="s">
+      <c r="B2" s="4"/>
+      <c r="C2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="4"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="7" t="s">
+      <c r="B3" s="4"/>
+      <c r="C3" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="8"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="9"/>
-      <c r="C4" s="10" t="s">
+      <c r="B4" s="10"/>
+      <c r="C4" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="10"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="11"/>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11"/>
-      <c r="J5" s="11"/>
+      <c r="A5" s="12"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
     </row>
     <row r="6" customFormat="false" ht="31.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="13"/>
-      <c r="E6" s="14" t="s">
+      <c r="D6" s="14"/>
+      <c r="E6" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="F6" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="G6" s="13" t="s">
+      <c r="G6" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="H6" s="15" t="s">
+      <c r="H6" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="I6" s="16" t="s">
+      <c r="I6" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="J6" s="16"/>
+      <c r="J6" s="17"/>
     </row>
     <row r="7" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="18"/>
-      <c r="C7" s="19" t="s">
+      <c r="B7" s="19"/>
+      <c r="C7" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="19"/>
-      <c r="H7" s="19"/>
-      <c r="I7" s="19"/>
-      <c r="J7" s="19"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="20"/>
+      <c r="G7" s="20"/>
+      <c r="H7" s="20"/>
+      <c r="I7" s="20"/>
+      <c r="J7" s="20"/>
     </row>
     <row r="8" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="20" t="n">
+      <c r="A8" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="C8" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="21"/>
-      <c r="E8" s="22" t="s">
+      <c r="D8" s="23"/>
+      <c r="E8" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="F8" s="23" t="s">
+      <c r="F8" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="G8" s="23"/>
-      <c r="H8" s="24"/>
-      <c r="I8" s="25"/>
-      <c r="J8" s="25"/>
+      <c r="G8" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="H8" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="I8" s="27"/>
+      <c r="J8" s="27"/>
     </row>
     <row r="9" customFormat="false" ht="46.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="20" t="n">
+      <c r="A9" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="B9" s="21" t="s">
+      <c r="B9" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" s="23"/>
+      <c r="E9" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="G9" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="H9" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="I9" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="J9" s="29"/>
+    </row>
+    <row r="10" customFormat="false" ht="46.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="22"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="30"/>
+      <c r="H10" s="31"/>
+      <c r="I10" s="32"/>
+      <c r="J10" s="33"/>
+    </row>
+    <row r="11" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="22"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="22"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="30"/>
+      <c r="H11" s="26"/>
+      <c r="I11" s="27"/>
+      <c r="J11" s="27"/>
+    </row>
+    <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="34" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="35"/>
+      <c r="C12" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="20"/>
+      <c r="I12" s="20"/>
+      <c r="J12" s="20"/>
+    </row>
+    <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" s="36"/>
+      <c r="E13" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="F13" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="G13" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="H13" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="I13" s="27"/>
+      <c r="J13" s="27"/>
+    </row>
+    <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="37" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" s="37"/>
+      <c r="E14" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="F14" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="G14" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="H14" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="I14" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="J14" s="29"/>
+    </row>
+    <row r="15" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="B15" s="22"/>
+      <c r="C15" s="38"/>
+      <c r="D15" s="38"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="26"/>
+      <c r="I15" s="27"/>
+      <c r="J15" s="27"/>
+    </row>
+    <row r="16" customFormat="false" ht="46.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="B16" s="22"/>
+      <c r="C16" s="38"/>
+      <c r="D16" s="38"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="22"/>
+      <c r="G16" s="22"/>
+      <c r="H16" s="26"/>
+      <c r="I16" s="32"/>
+      <c r="J16" s="33"/>
+    </row>
+    <row r="17" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="B17" s="22"/>
+      <c r="C17" s="39"/>
+      <c r="D17" s="39"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="22"/>
+      <c r="H17" s="26"/>
+      <c r="I17" s="27"/>
+      <c r="J17" s="27"/>
+    </row>
+    <row r="18" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="35"/>
+      <c r="C18" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="20"/>
+      <c r="I18" s="20"/>
+      <c r="J18" s="20"/>
+    </row>
+    <row r="19" customFormat="false" ht="31.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="B19" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="D19" s="36"/>
+      <c r="E19" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="F19" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="G19" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="H19" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="I19" s="27"/>
+      <c r="J19" s="27"/>
+    </row>
+    <row r="20" customFormat="false" ht="31.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20" s="37" t="s">
+        <v>49</v>
+      </c>
+      <c r="D20" s="37"/>
+      <c r="E20" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="F20" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="21" t="s">
+      <c r="G20" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="H20" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="21"/>
-      <c r="E9" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="F9" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="G9" s="23"/>
-      <c r="H9" s="24"/>
-      <c r="I9" s="25"/>
-      <c r="J9" s="25"/>
-    </row>
-    <row r="10" customFormat="false" ht="46.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="20" t="n">
+      <c r="I20" s="27"/>
+      <c r="J20" s="27"/>
+    </row>
+    <row r="21" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="B10" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="F10" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="G10" s="23"/>
-      <c r="H10" s="26"/>
-      <c r="I10" s="27"/>
-      <c r="J10" s="28"/>
-    </row>
-    <row r="11" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="20" t="n">
+      <c r="B21" s="22"/>
+      <c r="C21" s="38"/>
+      <c r="D21" s="38"/>
+      <c r="E21" s="22"/>
+      <c r="F21" s="22"/>
+      <c r="G21" s="22"/>
+      <c r="H21" s="26"/>
+      <c r="I21" s="27"/>
+      <c r="J21" s="27"/>
+    </row>
+    <row r="22" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="B11" s="21"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="21"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="23"/>
-      <c r="G11" s="23"/>
-      <c r="H11" s="24"/>
-      <c r="I11" s="25"/>
-      <c r="J11" s="25"/>
-    </row>
-    <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12" s="30"/>
-      <c r="C12" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
-      <c r="G12" s="19"/>
-      <c r="H12" s="19"/>
-      <c r="I12" s="19"/>
-      <c r="J12" s="19"/>
-    </row>
-    <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="B13" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="C13" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="D13" s="31"/>
-      <c r="E13" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="F13" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="G13" s="21"/>
-      <c r="H13" s="26"/>
-      <c r="I13" s="25"/>
-      <c r="J13" s="25"/>
-    </row>
-    <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="B14" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" s="32" t="s">
-        <v>34</v>
-      </c>
-      <c r="D14" s="32"/>
-      <c r="E14" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="F14" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="G14" s="21"/>
-      <c r="H14" s="24"/>
-      <c r="I14" s="25"/>
-      <c r="J14" s="25"/>
-    </row>
-    <row r="15" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="B15" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="C15" s="32" t="s">
-        <v>38</v>
-      </c>
-      <c r="D15" s="32"/>
-      <c r="E15" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="F15" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="G15" s="21"/>
-      <c r="H15" s="24"/>
-      <c r="I15" s="25"/>
-      <c r="J15" s="25"/>
-    </row>
-    <row r="16" customFormat="false" ht="46.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="B16" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="C16" s="32" t="s">
-        <v>42</v>
-      </c>
-      <c r="D16" s="32"/>
-      <c r="E16" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="F16" s="21" t="s">
-        <v>44</v>
-      </c>
-      <c r="G16" s="21"/>
-      <c r="H16" s="24"/>
-      <c r="I16" s="27"/>
-      <c r="J16" s="28"/>
-    </row>
-    <row r="17" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="20" t="n">
+      <c r="B22" s="22"/>
+      <c r="C22" s="38"/>
+      <c r="D22" s="38"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="26"/>
+      <c r="I22" s="32"/>
+      <c r="J22" s="33"/>
+    </row>
+    <row r="23" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="B17" s="21"/>
-      <c r="C17" s="31"/>
-      <c r="D17" s="31"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="21"/>
-      <c r="G17" s="21"/>
-      <c r="H17" s="24"/>
-      <c r="I17" s="25"/>
-      <c r="J17" s="25"/>
-    </row>
-    <row r="18" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="29" t="s">
-        <v>45</v>
-      </c>
-      <c r="B18" s="30"/>
-      <c r="C18" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="19"/>
-      <c r="I18" s="19"/>
-      <c r="J18" s="19"/>
-    </row>
-    <row r="19" customFormat="false" ht="31.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="B19" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="C19" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="D19" s="31"/>
-      <c r="E19" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="F19" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="G19" s="21"/>
-      <c r="H19" s="26"/>
-      <c r="I19" s="25"/>
-      <c r="J19" s="25"/>
-    </row>
-    <row r="20" customFormat="false" ht="31.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="B20" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="C20" s="32" t="s">
-        <v>51</v>
-      </c>
-      <c r="D20" s="32"/>
-      <c r="E20" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="F20" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="G20" s="21"/>
-      <c r="H20" s="24"/>
-      <c r="I20" s="25"/>
-      <c r="J20" s="25"/>
-    </row>
-    <row r="21" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="B21" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="C21" s="32" t="s">
-        <v>54</v>
-      </c>
-      <c r="D21" s="32"/>
-      <c r="E21" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="F21" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="G21" s="21"/>
-      <c r="H21" s="24"/>
-      <c r="I21" s="25"/>
-      <c r="J21" s="25"/>
-    </row>
-    <row r="22" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="B22" s="21"/>
-      <c r="C22" s="32"/>
-      <c r="D22" s="32"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="21"/>
-      <c r="G22" s="21"/>
-      <c r="H22" s="24"/>
-      <c r="I22" s="27"/>
-      <c r="J22" s="28"/>
-    </row>
-    <row r="23" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="B23" s="21"/>
-      <c r="C23" s="31"/>
-      <c r="D23" s="31"/>
-      <c r="E23" s="21"/>
-      <c r="F23" s="21"/>
-      <c r="G23" s="21"/>
-      <c r="H23" s="24"/>
-      <c r="I23" s="25"/>
-      <c r="J23" s="25"/>
+      <c r="B23" s="22"/>
+      <c r="C23" s="39"/>
+      <c r="D23" s="39"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="22"/>
+      <c r="G23" s="22"/>
+      <c r="H23" s="26"/>
+      <c r="I23" s="27"/>
+      <c r="J23" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="38">
